--- a/assets/box/xiafengbaonang/箱子概况.xlsx
+++ b/assets/box/xiafengbaonang/箱子概况.xlsx
@@ -1,74 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YJWJ\YJWJ\assets\box\xiafengbaonang\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6680C54-288C-49DB-8F6F-C2944581998F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16000" yWindow="6970" windowWidth="18710" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-16730" yWindow="7940" windowWidth="16370" windowHeight="13680" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>品质</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>图片名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>侠风宝囊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屏幕截图 2026-07-20 104645.png</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
+      <charset val="134"/>
       <family val="3"/>
-      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="8"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -86,25 +60,88 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -370,39 +407,615 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="19.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.75" bestFit="1" customWidth="1"/>
+    <col width="19.75" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
+    <col width="31.75" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>侠风宝囊</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>xiafengbaonang.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>品质</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>图片名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>寒梅傲雪</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>红</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>01.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>断昼呤</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>红</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>02.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>倾国倾城·闭月</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>03.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>倾国倾城·羞花</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>04.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>孤影戎装</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>05.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>胧月魂</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>06.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>折寒英</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>07.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【挑染】天涯醉</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>08.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【挑染】鸿影</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>09.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>墨影浮沉</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>10.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>古龙江湖·冷香痕</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>11.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>蛋筒猫猫</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>12.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>占有</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>13.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>寒刃千流</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>14.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>山青黛</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>15.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>洗心池</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>16.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>鱼皮甲·碧鲟</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>紫</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>17.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>绝命衣·胭</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>紫</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>18.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>倦客衫</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>紫</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>19.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>陷阵·怒涛</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>紫</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>20.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>撞钟槌·鎏</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>紫</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>21.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>虎目·钧紫</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>紫</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>22.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>镖客面巾</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>紫</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>23.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>萦金瓶</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>紫</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>24.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>军哨</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>紫</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>25.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>神术祭台·樱色</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>紫</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>26.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>朱砂山石</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>紫</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>27.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>倾国倾城·戟花恋</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>紫</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>28.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>倾国倾城·人间乐</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>紫</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>29.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>万钧·巴掌战神</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>紫</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>30.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>胡为·嗯？</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>紫</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>31.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>沈妙·机车</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>紫</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>32.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="192" customHeight="1" s="2">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>开启侠风宝囊获得奖励品质及概率分别为：
+基础概率：
+红色（神品）：0.6%
+金色（极品）：8%
+紫色（优品）：91.4%
+保底规则：
+循环保底：在基础概率的基础上，每开启至多100次，必可以获得一件红色（神品）品质的奖励，此保可以不限次数触发。
+在获得所有红色（神品）品质奖励之前，红色（神品）奖励不会重复获得。
+极品外观保底规则：
+开启25次以内必定获得一件极品英雄时装或武器皮肤，后续每25次以内必定获得一件未解锁的极品外观，极品外观保底一共可以触发14次。
+心愿极品奖励：
+每次抽中神品外观，将获得1次指定极品外观的机会。指定完成后，将在下次抽中极品外观时获得指定的外观。次数可以累积，但每次只能指定1个外观。
+当心愿极品奖励和极品外观保底同时触发后，优先触发心愿极品奖励，并消耗本次极品外观保底次数。</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A35:C35"/>
     <mergeCell ref="A1:B1"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>